--- a/database/event/5937/event_5937_evp_summary.xlsx
+++ b/database/event/5937/event_5937_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.7526</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.862500000000001</v>
+        <v>8.4107</v>
       </c>
       <c r="I2" t="n">
         <v>9.457800000000001</v>
@@ -538,7 +538,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -548,7 +548,7 @@
         <v>1.7526</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E3" t="n">
         <v>6.4635</v>
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8.225899999999999</v>
+        <v>10.7132</v>
       </c>
       <c r="I3" t="n">
-        <v>8.7784</v>
+        <v>12.047</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.7784</v>
+        <v>12.047</v>
       </c>
       <c r="N3" t="n">
         <v>575</v>
@@ -584,32 +584,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4635</v>
+        <v>6.4475</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7526</v>
+        <v>1.7483</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1897</v>
+        <v>2.1248</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4635</v>
+        <v>6.4475</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4635</v>
+        <v>6.4475</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>11.2888</v>
+        <v>7.8065</v>
       </c>
       <c r="I4" t="n">
-        <v>12.047</v>
+        <v>8.7784</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.047</v>
+        <v>8.7784</v>
       </c>
       <c r="N4" t="n">
         <v>575</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7718</v>
+        <v>5.5831</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5651</v>
+        <v>1.5139</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9103</v>
+        <v>1.7804</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7718</v>
+        <v>5.5831</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7718</v>
+        <v>5.5831</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7471</v>
+        <v>6.4512</v>
       </c>
       <c r="I5" t="n">
         <v>7.1337</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4153</v>
+        <v>5.2141</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4684</v>
+        <v>1.4138</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7663</v>
+        <v>1.6334</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4153</v>
+        <v>5.2141</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4153</v>
+        <v>5.2141</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1881</v>
+        <v>5.8726</v>
       </c>
       <c r="I6" t="n">
         <v>6.6037</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2717</v>
+        <v>5.0779</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4294</v>
+        <v>1.3769</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7083</v>
+        <v>1.5791</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2717</v>
+        <v>5.0779</v>
       </c>
       <c r="F7" t="n">
-        <v>5.2717</v>
+        <v>5.0779</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.963</v>
+        <v>5.659</v>
       </c>
       <c r="I7" t="n">
         <v>6.3635</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0967</v>
+        <v>4.9117</v>
       </c>
       <c r="C8" t="n">
-        <v>1.382</v>
+        <v>1.3318</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6376</v>
+        <v>1.5129</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0967</v>
+        <v>4.9117</v>
       </c>
       <c r="F8" t="n">
-        <v>5.0967</v>
+        <v>4.9117</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6885</v>
+        <v>5.3985</v>
       </c>
       <c r="I8" t="n">
         <v>6.0706</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.9454</v>
+        <v>4.8683</v>
       </c>
       <c r="C9" t="n">
-        <v>1.341</v>
+        <v>1.3201</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5765</v>
+        <v>1.4956</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9454</v>
+        <v>4.8683</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9454</v>
+        <v>4.8683</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4513</v>
+        <v>5.3304</v>
       </c>
       <c r="I9" t="n">
         <v>5.6053</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.4342</v>
+        <v>4.3042</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2024</v>
+        <v>1.1671</v>
       </c>
       <c r="D10" t="n">
-        <v>1.37</v>
+        <v>1.2709</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4342</v>
+        <v>4.3042</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4342</v>
+        <v>4.3042</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6498</v>
+        <v>4.4459</v>
       </c>
       <c r="I10" t="n">
         <v>4.9163</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6185</v>
+        <v>3.5251</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9812</v>
+        <v>0.9558</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0404</v>
+        <v>0.9605</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6185</v>
+        <v>3.5251</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6185</v>
+        <v>3.5251</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6185</v>
+        <v>3.5251</v>
       </c>
       <c r="I11" t="n">
         <v>3.7381</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5518</v>
+        <v>3.486</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9631</v>
+        <v>0.9452</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0135</v>
+        <v>0.9449</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5518</v>
+        <v>3.486</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5518</v>
+        <v>3.486</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5518</v>
+        <v>3.486</v>
       </c>
       <c r="I12" t="n">
         <v>3.6352</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4598</v>
+        <v>3.2834</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9381</v>
+        <v>0.8903</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.8642</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4598</v>
+        <v>3.2834</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4598</v>
+        <v>3.2834</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4598</v>
+        <v>3.2834</v>
       </c>
       <c r="I13" t="n">
         <v>3.6922</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9035</v>
+        <v>2.7762</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7873</v>
+        <v>0.7528</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7516</v>
+        <v>0.6621</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9035</v>
+        <v>2.7762</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9035</v>
+        <v>2.7762</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9035</v>
+        <v>2.7762</v>
       </c>
       <c r="I14" t="n">
         <v>3.0699</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.436</v>
+        <v>2.382</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6605</v>
+        <v>0.6459</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5627</v>
+        <v>0.5051</v>
       </c>
       <c r="E15" t="n">
-        <v>2.436</v>
+        <v>2.382</v>
       </c>
       <c r="F15" t="n">
-        <v>2.436</v>
+        <v>2.382</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.436</v>
+        <v>2.382</v>
       </c>
       <c r="I15" t="n">
         <v>2.5048</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2919</v>
+        <v>2.2579</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6122</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4556</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2919</v>
+        <v>2.2579</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2919</v>
+        <v>2.2579</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2919</v>
+        <v>2.2579</v>
       </c>
       <c r="I16" t="n">
         <v>2.3349</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1138</v>
+        <v>2.0669</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5732</v>
+        <v>0.5605</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4326</v>
+        <v>0.3795</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1138</v>
+        <v>2.0669</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1138</v>
+        <v>2.0669</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1138</v>
+        <v>2.0669</v>
       </c>
       <c r="I17" t="n">
         <v>2.1735</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5666</v>
+        <v>1.5376</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4248</v>
+        <v>0.4169</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2115</v>
+        <v>0.1687</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5666</v>
+        <v>1.5376</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5666</v>
+        <v>1.5376</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5666</v>
+        <v>1.5376</v>
       </c>
       <c r="I18" t="n">
         <v>1.6034</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5533</v>
+        <v>1.5302</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4212</v>
+        <v>0.4149</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2061</v>
+        <v>0.1657</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5533</v>
+        <v>1.5302</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5533</v>
+        <v>1.5302</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5533</v>
+        <v>1.5302</v>
       </c>
       <c r="I19" t="n">
         <v>1.5824</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3946</v>
+        <v>1.3739</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3782</v>
+        <v>0.3725</v>
       </c>
       <c r="D20" t="n">
-        <v>0.142</v>
+        <v>0.1035</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3946</v>
+        <v>1.3739</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3946</v>
+        <v>1.3739</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3946</v>
+        <v>1.3739</v>
       </c>
       <c r="I20" t="n">
         <v>1.4207</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3899</v>
+        <v>1.3693</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3769</v>
+        <v>0.3713</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1401</v>
+        <v>0.1016</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3899</v>
+        <v>1.3693</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3899</v>
+        <v>1.3693</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3899</v>
+        <v>1.3693</v>
       </c>
       <c r="I21" t="n">
         <v>1.416</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1989</v>
+        <v>1.1463</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3251</v>
+        <v>0.3108</v>
       </c>
       <c r="D22" t="n">
-        <v>0.063</v>
+        <v>0.0128</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1989</v>
+        <v>1.1463</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1989</v>
+        <v>1.1463</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1989</v>
+        <v>1.1463</v>
       </c>
       <c r="I22" t="n">
         <v>1.2676</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0855</v>
+        <v>1.0694</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2943</v>
+        <v>0.29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0172</v>
+        <v>-0.0179</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0855</v>
+        <v>1.0694</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0855</v>
+        <v>1.0694</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0855</v>
+        <v>1.0694</v>
       </c>
       <c r="I23" t="n">
         <v>1.1059</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0145</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2751</v>
+        <v>0.271</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0115</v>
+        <v>-0.0457</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0145</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0145</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0145</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>1.0336</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8718</v>
+        <v>0.8273</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2364</v>
+        <v>0.2243</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0692</v>
+        <v>-0.1143</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8718</v>
+        <v>0.8273</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8718</v>
+        <v>0.8273</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8718</v>
+        <v>0.8273</v>
       </c>
       <c r="I25" t="n">
         <v>0.9303</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8134</v>
+        <v>0.8013</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2206</v>
+        <v>0.2173</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1247</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8134</v>
+        <v>0.8013</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8134</v>
+        <v>0.8013</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8134</v>
+        <v>0.8013</v>
       </c>
       <c r="I26" t="n">
         <v>0.8286</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7099</v>
+        <v>0.6994</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1925</v>
+        <v>0.1896</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1346</v>
+        <v>-0.1653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7099</v>
+        <v>0.6994</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7099</v>
+        <v>0.6994</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7099</v>
+        <v>0.6994</v>
       </c>
       <c r="I27" t="n">
         <v>0.7232</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5657</v>
+        <v>0.5511</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1534</v>
+        <v>0.1494</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1928</v>
+        <v>-0.2244</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5657</v>
+        <v>0.5511</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5657</v>
+        <v>0.5511</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5657</v>
+        <v>0.5511</v>
       </c>
       <c r="I28" t="n">
         <v>0.5844</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4682</v>
+        <v>0.4613</v>
       </c>
       <c r="C29" t="n">
-        <v>0.127</v>
+        <v>0.1251</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2322</v>
+        <v>-0.2601</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4682</v>
+        <v>0.4613</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4682</v>
+        <v>0.4613</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4682</v>
+        <v>0.4613</v>
       </c>
       <c r="I29" t="n">
         <v>0.477</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3272</v>
+        <v>0.3221</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0887</v>
+        <v>0.0873</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2892</v>
+        <v>-0.3156</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3272</v>
+        <v>0.3221</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3272</v>
+        <v>0.3221</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3272</v>
+        <v>0.3221</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3492</v>
+        <v>0.333</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>575</v>
+        <v>315</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3492</v>
+        <v>0.333</v>
       </c>
       <c r="N30" t="n">
-        <v>575</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3269</v>
+        <v>0.3105</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0886</v>
+        <v>0.0842</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2893</v>
+        <v>-0.3202</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3269</v>
+        <v>0.3105</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3269</v>
+        <v>0.3105</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3269</v>
+        <v>0.3105</v>
       </c>
       <c r="I31" t="n">
-        <v>0.333</v>
+        <v>0.3492</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>315</v>
+        <v>575</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.333</v>
+        <v>0.3492</v>
       </c>
       <c r="N31" t="n">
-        <v>315</v>
+        <v>575</v>
       </c>
     </row>
     <row r="32">
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.3137</v>
+        <v>0.3068</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0851</v>
+        <v>0.0832</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2946</v>
+        <v>-0.3217</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3137</v>
+        <v>0.3068</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3137</v>
+        <v>0.3068</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3137</v>
+        <v>0.3068</v>
       </c>
       <c r="I32" t="n">
         <v>0.3226</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0331</v>
+        <v>0.0325</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.408</v>
+        <v>-0.431</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0331</v>
+        <v>0.0325</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0331</v>
+        <v>0.0325</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0331</v>
+        <v>0.0325</v>
       </c>
       <c r="I33" t="n">
         <v>0.0339</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0229</v>
+        <v>0.0223</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0062</v>
+        <v>0.006</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4121</v>
+        <v>-0.435</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0229</v>
+        <v>0.0223</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0229</v>
+        <v>0.0223</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0229</v>
+        <v>0.0223</v>
       </c>
       <c r="I34" t="n">
         <v>0.0236</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0004</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.422</v>
+        <v>-0.4445</v>
       </c>
       <c r="E35" t="n">
         <v>-0.0016</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3093</v>
+        <v>-0.3047</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0839</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5463</v>
+        <v>-0.5653</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3093</v>
+        <v>-0.3047</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3093</v>
+        <v>-0.3047</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3093</v>
+        <v>-0.3047</v>
       </c>
       <c r="I36" t="n">
         <v>-0.3151</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.523</v>
+        <v>-0.4963</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1418</v>
+        <v>-0.1346</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.523</v>
+        <v>-0.4963</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.523</v>
+        <v>-0.4963</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.523</v>
+        <v>-0.4963</v>
       </c>
       <c r="I37" t="n">
         <v>-0.5581</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6186</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1715</v>
+        <v>-0.1677</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6904</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6186</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6186</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6186</v>
       </c>
       <c r="I38" t="n">
         <v>-0.6505</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.6461</v>
+        <v>-0.6294</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1752</v>
+        <v>-0.1707</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.6824</v>
+        <v>-0.6947</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6461</v>
+        <v>-0.6294</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6461</v>
+        <v>-0.6294</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6461</v>
+        <v>-0.6294</v>
       </c>
       <c r="I39" t="n">
         <v>-0.6674</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8118</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2243</v>
+        <v>-0.2201</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7673</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8118</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8118</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8118</v>
       </c>
       <c r="I40" t="n">
         <v>-0.8465</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.9326</v>
+        <v>-0.9291</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2529</v>
+        <v>-0.2519</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.7981</v>
+        <v>-0.8141</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.9326</v>
+        <v>-0.9291</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9326</v>
+        <v>-0.9291</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9326</v>
+        <v>-0.9291</v>
       </c>
       <c r="I41" t="n">
         <v>-0.9369</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.4201</v>
+        <v>-1.399</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.3851</v>
+        <v>-0.3793</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.9951</v>
+        <v>-1.0013</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.4201</v>
+        <v>-1.399</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.4201</v>
+        <v>-1.399</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.4201</v>
+        <v>-1.399</v>
       </c>
       <c r="I42" t="n">
         <v>-1.4467</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-1.4756</v>
+        <v>-1.4109</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.4001</v>
+        <v>-0.3826</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.0175</v>
+        <v>-1.006</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.4756</v>
+        <v>-1.4109</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.4756</v>
+        <v>-1.4109</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.4756</v>
+        <v>-1.4109</v>
       </c>
       <c r="I43" t="n">
         <v>-1.5602</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-1.4849</v>
+        <v>-1.4628</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.4026</v>
+        <v>-0.3966</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.0212</v>
+        <v>-1.0267</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.4849</v>
+        <v>-1.4628</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.4849</v>
+        <v>-1.4628</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.4849</v>
+        <v>-1.4628</v>
       </c>
       <c r="I44" t="n">
         <v>-1.5127</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-2.0105</v>
+        <v>-2.003</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.5452</v>
+        <v>-0.5431</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.2336</v>
+        <v>-1.2419</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.0105</v>
+        <v>-2.003</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.0105</v>
+        <v>-2.003</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.0105</v>
+        <v>-2.003</v>
       </c>
       <c r="I45" t="n">
         <v>-2.0199</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-2.7642</v>
+        <v>-2.7539</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7467</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.538</v>
+        <v>-1.5411</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.7642</v>
+        <v>-2.7539</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.7642</v>
+        <v>-2.7539</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.7642</v>
+        <v>-2.7539</v>
       </c>
       <c r="I46" t="n">
         <v>-2.7771</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-2.9166</v>
+        <v>-2.8733</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.7909</v>
+        <v>-0.7791</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.5996</v>
+        <v>-1.5886</v>
       </c>
       <c r="E47" t="n">
-        <v>-2.9166</v>
+        <v>-2.8733</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.9166</v>
+        <v>-2.8733</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.9166</v>
+        <v>-2.8733</v>
       </c>
       <c r="I47" t="n">
         <v>-2.9713</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.9439</v>
+        <v>-2.8894</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.7983</v>
+        <v>-0.7835</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.6106</v>
+        <v>-1.595</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.9439</v>
+        <v>-2.8894</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.9439</v>
+        <v>-2.8894</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.9439</v>
+        <v>-2.8894</v>
       </c>
       <c r="I48" t="n">
         <v>-3.0131</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-3.1183</v>
+        <v>-3.1067</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.8455</v>
+        <v>-0.8424</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.6811</v>
+        <v>-1.6816</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.1183</v>
+        <v>-3.1067</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.1183</v>
+        <v>-3.1067</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.1183</v>
+        <v>-3.1067</v>
       </c>
       <c r="I49" t="n">
         <v>-3.1328</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-3.1599</v>
+        <v>-3.113</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.8568</v>
+        <v>-0.8441</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.6979</v>
+        <v>-1.6841</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.1599</v>
+        <v>-3.113</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.1599</v>
+        <v>-3.113</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.1599</v>
+        <v>-3.113</v>
       </c>
       <c r="I50" t="n">
         <v>-3.2191</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-4.8668</v>
+        <v>-4.7411</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.3197</v>
+        <v>-1.2856</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.3874</v>
+        <v>-2.3328</v>
       </c>
       <c r="E51" t="n">
-        <v>-4.8668</v>
+        <v>-4.7411</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.8668</v>
+        <v>-4.7411</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.8668</v>
+        <v>-4.7411</v>
       </c>
       <c r="I51" t="n">
         <v>-5.0276</v>
